--- a/data/trans_orig/P43B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43B-Clase-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha mamografía en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última mamografía en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35436</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58762</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>47573</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>35436</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>58762</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>35,66%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>44,05%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85818</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74629</t>
+          <t>73809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97955</t>
+          <t>96387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>85818</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>74629</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>97955</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>64,34%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>73,43%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>133391</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>133391</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>133391</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44849</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33096</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>58462</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>44849</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>33096</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>56505</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>35,72%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>26,36%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80706</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69050</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92459</t>
+          <t>91586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>80706</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>69050</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>92459</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>64,28%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>55,0%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>73,64%</t>
+          <t>72,95%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125555</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125555</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>125555</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>125555</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>125555</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>21846</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>14416</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>33131</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>24,83%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111602</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100317</t>
+          <t>100895</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119032</t>
+          <t>119561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>111602</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>100317</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>119032</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>83,63%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>75,17%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>133448</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>133448</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>133448</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42045</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56379</t>
+          <t>55880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>42045</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>30972</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>56379</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253371</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239037</t>
+          <t>239536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>264444</t>
+          <t>265400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>253371</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>239037</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>264444</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>80,92%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>295416</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>295416</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>295416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>295416</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>295416</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>295416</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2094,37 +1614,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23082</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>45571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,47 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>32204</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>23082</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>45123</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -2207,37 +1692,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355547</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>365556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342628</t>
+          <t>342180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>364669</t>
+          <t>365556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,47 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>355547</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>342628</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>364669</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>88,36%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -2320,37 +1770,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387751</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387751</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2384,41 +1834,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>387751</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>387751</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>387751</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2437,37 +1852,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34464</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61277</t>
+          <t>59275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,47 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>45519</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>34464</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>61277</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -2550,37 +1930,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>511459</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>497703</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>495701</t>
+          <t>497703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>522514</t>
+          <t>524203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,47 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>511459</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>495701</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>522514</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2008,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>518</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>556978</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>556978</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>556978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2727,41 +2072,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>556978</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>556978</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>556978</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2780,37 +2090,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234035</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205751</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205497</t>
+          <t>205751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265687</t>
+          <t>265635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,45 +2150,10 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>234035</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>205497</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>265687</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>16,27%</t>
         </is>
@@ -2893,37 +2168,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1398505</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1366905</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1426789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1366853</t>
+          <t>1366905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1427043</t>
+          <t>1426789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,42 +2233,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1398505</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1366853</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1427043</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -3006,37 +2246,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1632540</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1632540</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1632540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3070,41 +2310,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1491</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1632540</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1632540</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1632540</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3118,7 +2323,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3126,7 +2331,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3141,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3160,25 +2364,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha mamografía en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última mamografía en 2016 (tasa de respuesta: 96,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +2386,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3198,17 +2395,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3279,41 +2465,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3336,13 +2487,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3357,37 +2501,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50363</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39178</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +2546,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38202</t>
+          <t>39178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63824</t>
+          <t>63505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,47 +2561,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>50363</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>38202</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>63824</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>30,56%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -3470,37 +2579,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114433</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +2624,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100972</t>
+          <t>101291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126594</t>
+          <t>125618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,47 +2639,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>114433</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>100972</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>126594</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>69,44%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>76,82%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -3583,37 +2657,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164796</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164796</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3647,41 +2721,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>164796</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>164796</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>164796</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3700,37 +2739,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46268</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +2784,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35301</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58485</t>
+          <t>57860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,47 +2799,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>46268</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>35301</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>58485</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -3813,37 +2817,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124484</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +2862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112267</t>
+          <t>112892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135451</t>
+          <t>136524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,47 +2877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>124484</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>112267</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>135451</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>72,9%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>79,33%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -3926,37 +2895,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170752</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170752</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3990,41 +2959,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>170752</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>170752</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>170752</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4043,37 +2977,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +3022,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,47 +3037,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12707</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7152</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>19683</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -4156,37 +3055,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75915</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +3100,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68939</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81470</t>
+          <t>81803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,47 +3115,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>75915</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>68939</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>81470</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>77,79%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -4269,37 +3133,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88622</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4333,41 +3197,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>88622</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>88622</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>88622</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4386,37 +3215,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +3260,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,47 +3275,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>32081</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>44640</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -4499,37 +3293,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287796</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +3338,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275237</t>
+          <t>275533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297025</t>
+          <t>298106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,47 +3353,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>287796</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>275237</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>297025</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>89,97%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>86,04%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -4612,37 +3371,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>297</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319877</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319877</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4676,41 +3435,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>319877</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>319877</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>319877</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4729,37 +3453,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +3498,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30522</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,47 +3513,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>18905</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>12020</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>30522</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -4842,37 +3531,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379041</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +3576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>367424</t>
+          <t>369473</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>385926</t>
+          <t>387351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,47 +3591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>379041</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>367424</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>385926</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -4955,37 +3609,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>362</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397946</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397946</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397946</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5019,41 +3673,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>397946</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>397946</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>397946</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5072,37 +3691,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48024</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63521</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +3736,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35656</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64517</t>
+          <t>63521</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,47 +3751,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>48024</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>35656</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>64517</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -5185,37 +3769,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>439</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>495288</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>479791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>507968</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +3814,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>478795</t>
+          <t>479791</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>507656</t>
+          <t>507968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,47 +3829,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>495288</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>478795</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>507656</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -5298,37 +3847,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>543312</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>543312</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>543312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5362,41 +3911,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>543312</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>543312</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>543312</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5415,37 +3929,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208349</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +3974,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180861</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>235738</t>
+          <t>236276</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,47 +3989,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>208349</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>180861</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>235738</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -5528,37 +4007,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1476957</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1449030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1503381</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +4052,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1449568</t>
+          <t>1449030</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1504445</t>
+          <t>1503381</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,47 +4067,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1476957</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1449568</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1504445</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -5641,37 +4085,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1685306</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1685306</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1685306</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5705,41 +4149,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1685306</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1685306</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1685306</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5753,7 +4162,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5761,7 +4170,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -5776,7 +4184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5795,25 +4203,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha mamografía en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última mamografía en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +4225,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5833,17 +4234,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5914,41 +4304,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5971,13 +4326,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5992,37 +4340,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84692</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +4385,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73372</t>
+          <t>74176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95962</t>
+          <t>95088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,47 +4400,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>84692</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>73372</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>95962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>44,78%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>38,8%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>50,74%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -6105,37 +4418,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>188</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104416</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +4463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93146</t>
+          <t>94020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115736</t>
+          <t>114932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,47 +4478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>104416</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>93146</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>115736</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>55,22%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>49,26%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>61,2%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -6218,37 +4496,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189108</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6282,41 +4560,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>189108</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>189108</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>189108</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6335,37 +4578,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59011</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +4623,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48284</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69516</t>
+          <t>69875</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,47 +4638,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>59011</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>48284</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>69516</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>35,6%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>41,94%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -6448,37 +4656,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>184</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106753</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +4701,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96248</t>
+          <t>95889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117480</t>
+          <t>116323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,47 +4716,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>106753</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>96248</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>117480</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>58,06%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>70,87%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -6561,37 +4734,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165764</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165764</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6625,41 +4798,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>165764</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>165764</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>165764</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6678,37 +4816,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +4861,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,47 +4876,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12053</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7129</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>17801</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>23,37%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -6791,37 +4894,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64129</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +4939,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58381</t>
+          <t>58568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,47 +4954,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>64129</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>58381</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>69053</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>84,18%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>76,63%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>90,64%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -6904,37 +4972,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6968,41 +5036,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>76182</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>76182</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>76182</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7021,37 +5054,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36371</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +5099,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68844</t>
+          <t>69048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,47 +5114,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>36371</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>12715</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>68844</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -7134,37 +5132,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>446</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444605</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>411928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>469288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +5177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>412132</t>
+          <t>411928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>468261</t>
+          <t>469288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,47 +5192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>444605</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>412132</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>468261</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -7247,37 +5210,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>507</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480976</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480976</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7311,41 +5274,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>480976</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>480976</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>480976</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7364,37 +5292,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +5337,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>29339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,47 +5352,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>20032</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>12995</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>31246</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -7477,37 +5370,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>335885</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +5415,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324671</t>
+          <t>326578</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342922</t>
+          <t>343214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,47 +5430,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>335885</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>324671</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>342922</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -7590,37 +5448,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355917</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7654,41 +5512,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>355917</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>355917</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>355917</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7707,37 +5530,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +5575,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,47 +5590,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>23471</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>17363</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>31952</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -7820,37 +5608,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>501</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261691</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>268054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +5653,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253210</t>
+          <t>253504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267799</t>
+          <t>268054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,47 +5668,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>261691</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>253210</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>267799</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -7933,37 +5686,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285162</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285162</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285162</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7997,41 +5750,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>285162</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>285162</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>285162</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8050,37 +5768,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>388</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235630</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +5813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149106</t>
+          <t>150111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>281431</t>
+          <t>283906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,47 +5828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>235630</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>149106</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>281431</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -8163,37 +5846,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1317480</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1269204</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1402999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +5891,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1271679</t>
+          <t>1269204</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1404004</t>
+          <t>1402999</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,47 +5906,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1317480</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1271679</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1404004</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>84,83%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>81,88%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -8276,37 +5924,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1553110</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1553110</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1553110</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8340,41 +5988,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2413</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1553110</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1553110</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1553110</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8388,7 +6001,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8396,7 +6009,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P43B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43B-Clase-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>60122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>60122</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73809</t>
+          <t>73269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96387</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73809</t>
+          <t>73269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96387</t>
+          <t>97067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,77%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58462</t>
+          <t>58257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58462</t>
+          <t>58257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67093</t>
+          <t>67298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91586</t>
+          <t>92642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67093</t>
+          <t>67298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91586</t>
+          <t>92642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>31880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100895</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119561</t>
+          <t>119586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100895</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119561</t>
+          <t>119586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55880</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30016</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55880</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239536</t>
+          <t>239831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265400</t>
+          <t>264680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239536</t>
+          <t>239831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265400</t>
+          <t>264680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>342180</t>
+          <t>342926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>365556</t>
+          <t>365476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342180</t>
+          <t>342926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365556</t>
+          <t>365476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32775</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59275</t>
+          <t>61886</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32775</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59275</t>
+          <t>61886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>497703</t>
+          <t>495092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>524203</t>
+          <t>524635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>497703</t>
+          <t>495092</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>524203</t>
+          <t>524635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205751</t>
+          <t>204437</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>265635</t>
+          <t>263225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205751</t>
+          <t>204437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265635</t>
+          <t>263225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1366905</t>
+          <t>1369315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1426789</t>
+          <t>1428103</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1366905</t>
+          <t>1369315</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1426789</t>
+          <t>1428103</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39178</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63505</t>
+          <t>63677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39178</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63505</t>
+          <t>63677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -2589,12 +2589,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101291</t>
+          <t>101119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125618</t>
+          <t>126138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101291</t>
+          <t>101119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125618</t>
+          <t>126138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112892</t>
+          <t>111967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>136524</t>
+          <t>136239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112892</t>
+          <t>111967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136524</t>
+          <t>136239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81803</t>
+          <t>80804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81803</t>
+          <t>80804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44344</t>
+          <t>45450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44344</t>
+          <t>45450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3303,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275533</t>
+          <t>274427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298106</t>
+          <t>297475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275533</t>
+          <t>274427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>298106</t>
+          <t>297475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369473</t>
+          <t>368684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387351</t>
+          <t>386544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>369473</t>
+          <t>368684</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387351</t>
+          <t>386544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>35454</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63521</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>35454</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63521</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>479791</t>
+          <t>478898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>507968</t>
+          <t>507858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>479791</t>
+          <t>478898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>507968</t>
+          <t>507858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181925</t>
+          <t>182022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>236276</t>
+          <t>237421</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181925</t>
+          <t>182022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236276</t>
+          <t>237421</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1449030</t>
+          <t>1447885</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1503381</t>
+          <t>1503284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1449030</t>
+          <t>1447885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1503381</t>
+          <t>1503284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84692</t>
+          <t>92856</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74176</t>
+          <t>81902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95088</t>
+          <t>105495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4380,32 +4380,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>84692</t>
+          <t>92856</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74176</t>
+          <t>81902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95088</t>
+          <t>105495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -4423,32 +4423,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>104416</t>
+          <t>116372</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94020</t>
+          <t>103733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114932</t>
+          <t>127326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4458,32 +4458,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>104416</t>
+          <t>116372</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94020</t>
+          <t>103733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114932</t>
+          <t>127326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59011</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69875</t>
+          <t>76044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59011</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69875</t>
+          <t>76044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -4661,32 +4661,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>119544</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95889</t>
+          <t>108122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116323</t>
+          <t>130033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>119544</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95889</t>
+          <t>108122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116323</t>
+          <t>130033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -4739,17 +4739,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -4899,32 +4899,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64129</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58568</t>
+          <t>64154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>74220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4934,32 +4934,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64129</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58568</t>
+          <t>64154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>74220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -4977,17 +4977,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5012,17 +5012,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5059,32 +5059,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69048</t>
+          <t>52192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5094,32 +5094,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69048</t>
+          <t>52192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -5137,32 +5137,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>444605</t>
+          <t>259652</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>411928</t>
+          <t>248573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>469288</t>
+          <t>268501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5172,32 +5172,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>444605</t>
+          <t>259652</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411928</t>
+          <t>248573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>469288</t>
+          <t>268501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -5215,17 +5215,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5250,17 +5250,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5297,32 +5297,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5332,32 +5332,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -5375,32 +5375,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>335885</t>
+          <t>327581</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326578</t>
+          <t>318258</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343214</t>
+          <t>334616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5410,32 +5410,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>335885</t>
+          <t>327581</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326578</t>
+          <t>318258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>343214</t>
+          <t>334616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -5453,17 +5453,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5535,32 +5535,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31658</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5570,32 +5570,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>18459</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31658</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -5613,32 +5613,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>261691</t>
+          <t>281537</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253504</t>
+          <t>271741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268054</t>
+          <t>288806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5648,32 +5648,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>261691</t>
+          <t>281537</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253504</t>
+          <t>271741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268054</t>
+          <t>288806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -5691,17 +5691,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>285162</t>
+          <t>307265</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>285162</t>
+          <t>307265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>285162</t>
+          <t>307265</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>285162</t>
+          <t>307265</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>285162</t>
+          <t>307265</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>285162</t>
+          <t>307265</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5773,32 +5773,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>235630</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150111</t>
+          <t>235725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>283906</t>
+          <t>282346</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5808,32 +5808,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>235630</t>
+          <t>259014</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150111</t>
+          <t>235725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283906</t>
+          <t>282346</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -5851,32 +5851,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1317480</t>
+          <t>1174153</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1269204</t>
+          <t>1150821</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1402999</t>
+          <t>1197442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1317480</t>
+          <t>1174153</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1269204</t>
+          <t>1150821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1402999</t>
+          <t>1197442</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -5929,17 +5929,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1553110</t>
+          <t>1433167</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1553110</t>
+          <t>1433167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1553110</t>
+          <t>1433167</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5964,17 +5964,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1553110</t>
+          <t>1433167</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1553110</t>
+          <t>1433167</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1553110</t>
+          <t>1433167</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
